--- a/data/raw/inventory/Week 28/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -780,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -795,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -842,10 +830,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -860,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -969,7 +957,7 @@
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -981,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>49</v>
@@ -1031,7 +1019,7 @@
         <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1043,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>20</v>
@@ -1090,13 +1078,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1108,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1214,10 +1202,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1232,7 +1220,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1338,7 +1326,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -1353,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1400,25 +1388,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>48</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>49</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1586,13 +1574,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
         <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1604,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1710,7 +1698,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -1725,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1772,13 +1760,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="F22" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1787,13 +1775,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1896,7 +1884,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -1911,10 +1899,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1958,13 +1946,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1976,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2147,7 +2135,7 @@
         <v>79</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
         <v>43</v>
@@ -2159,13 +2147,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2581,19 +2569,19 @@
         <v>204</v>
       </c>
       <c r="F35" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
         <v>215</v>

--- a/data/raw/inventory/Week 28/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>30</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
         <v>51</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>45</v>
@@ -969,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>17</v>
@@ -1034,13 +1034,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>13</v>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>48</v>
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
         <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1654,10 +1654,10 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1760,28 +1760,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F23" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1840,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L28" t="n">
         <v>18</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
         <v>13</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" t="n">
         <v>94</v>
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L30" t="n">
         <v>7</v>
@@ -2318,25 +2318,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -2569,7 +2569,7 @@
         <v>204</v>
       </c>
       <c r="F35" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
         <v>215</v>
